--- a/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="5" r:id="rId1"/>
@@ -1038,31 +1038,33 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A10" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B10" s="22">
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H10" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>229.07545878243178</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="4"/>
+        <v>1170.9245412175683</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="5"/>
+        <v>10253.395313505431</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>9746.6046864945693</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>8</v>
@@ -1072,102 +1074,108 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46204</v>
+      </c>
+      <c r="B11" s="23">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>205.59659265386028</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="4"/>
+        <v>1194.4034073461398</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="5"/>
+        <v>9058.9919061592918</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>10941.008093840708</v>
       </c>
       <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B12" s="22">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H12" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>181.6469385835567</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="4"/>
+        <v>1218.3530614164433</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="5"/>
+        <v>7840.638844742849</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="2"/>
+        <v>12159.361155257151</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46204</v>
+      </c>
+      <c r="B13" s="23">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>157.21705653788118</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="4"/>
+        <v>1242.7829434621187</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="5"/>
+        <v>6597.85590128073</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>13402.144098719269</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>12600</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1202,7 +1210,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>11424.319854722999</v>
+        <v>6597.85590128073</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1237,7 +1245,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>8575.6801452770014</v>
+        <v>13402.144098719269</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1469,31 +1477,33 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="22" t="str">
+      <c r="A4" s="2">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>180.28391146199303</v>
+      </c>
+      <c r="F4" s="1">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
+        <v>519.71608853800694</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>8471.2997110135693</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>1528.7002889864307</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>11</v>
@@ -1762,7 +1772,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1797,7 +1807,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>10500</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1832,7 +1842,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8991.0157995515765</v>
+        <v>8471.2997110135693</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1867,7 +1877,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1008.9842004484235</v>
+        <v>1528.7002889864307</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1175,42 +1175,44 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>7000</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B14" s="22">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H14" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
+        <v>132.29731719577319</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="4"/>
+        <v>1267.7026828042267</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="5"/>
+        <v>5330.1532184765038</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="2"/>
+        <v>14669.846781523496</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>6597.85590128073</v>
+        <v>5330.1532184765038</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1245,7 +1247,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>13402.144098719269</v>
+        <v>14669.846781523496</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>5600</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1212,42 +1212,44 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>5330.1532184765038</v>
+        <v>4037.031116629747</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46213</v>
+      </c>
+      <c r="B15" s="23">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>106.87789815324335</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="4"/>
+        <v>1293.1221018467566</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="5"/>
+        <v>4037.031116629747</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>15962.968883370253</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>5</v>
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>14669.846781523496</v>
+        <v>15962.968883370253</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>4200</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>4037.031116629747</v>
+        <v>2717.9798966815056</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1249,35 +1249,37 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>15962.968883370253</v>
+        <v>17282.020103318493</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B16" s="22">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G16" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H16" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="1"/>
+        <v>80.948780051758717</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="4"/>
+        <v>1319.0512199482414</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="5"/>
+        <v>2717.9798966815056</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="2"/>
+        <v>17282.020103318493</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>

--- a/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>2800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>2717.9798966815056</v>
+        <v>9.1336005425546318E-10</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>17282.020103318493</v>
+        <v>19999.999999999087</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1290,31 +1290,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46227</v>
+      </c>
+      <c r="B17" s="23">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>54.499742628996877</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="4"/>
+        <v>1345.500257371003</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="5"/>
+        <v>1372.4796393105025</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>18627.520360689497</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -1325,31 +1327,33 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B18" s="22">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G18" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H18" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="1"/>
+        <v>27.520360690410925</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="4"/>
+        <v>1372.4796393095892</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="5"/>
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="2"/>
+        <v>19999.999999999087</v>
       </c>
     </row>
   </sheetData>

--- a/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="5" r:id="rId1"/>
@@ -1521,31 +1521,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A5" s="19">
+        <v>46242</v>
+      </c>
+      <c r="B5" s="23">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>169.86279204898605</v>
+      </c>
+      <c r="F5" s="21">
+        <f t="shared" si="4"/>
+        <v>530.13720795101392</v>
+      </c>
+      <c r="G5" s="21">
+        <f t="shared" si="5"/>
+        <v>7941.1625030625555</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>2058.8374969374445</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -1553,31 +1555,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46242</v>
+      </c>
+      <c r="B6" s="22">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>159.23271291313185</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="4"/>
+        <v>540.76728708686812</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="5"/>
+        <v>7400.3952159756873</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>2599.6047840243127</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -1585,31 +1589,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46248</v>
+      </c>
+      <c r="B7" s="23">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>148.38948408557562</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" si="4"/>
+        <v>551.61051591442435</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="5"/>
+        <v>6848.7847000612628</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>3151.2152999387372</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -1619,31 +1625,33 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B8" s="22">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H8" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>137.328831582042</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="4"/>
+        <v>562.67116841795803</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="5"/>
+        <v>6286.1135316433047</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>3713.8864683566953</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>14</v>
@@ -1654,31 +1662,33 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A9" s="19">
+        <v>46255</v>
+      </c>
+      <c r="B9" s="23">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>126.0463957181946</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="4"/>
+        <v>573.95360428180538</v>
+      </c>
+      <c r="G9" s="21">
+        <f t="shared" si="5"/>
+        <v>5712.1599273614993</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>4287.8400726385007</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>7</v>
@@ -1688,31 +1698,33 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A10" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="22">
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H10" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>114.53772939121589</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="4"/>
+        <v>585.46227060878414</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="5"/>
+        <v>5126.6976567527154</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>4873.3023432472846</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>8</v>
@@ -1782,7 +1794,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1817,7 +1829,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>9800</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1852,7 +1864,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8471.2997110135693</v>
+        <v>5126.6976567527154</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1887,7 +1899,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1528.7002889864307</v>
+        <v>4873.3023432472846</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Bidyarani_Weekly.xlsx
@@ -1734,137 +1734,145 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46262</v>
+      </c>
+      <c r="B11" s="23">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>102.79829632693014</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="4"/>
+        <v>597.20170367306991</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="5"/>
+        <v>4529.4959530796459</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>5470.5040469203541</v>
       </c>
       <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B12" s="22">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H12" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>90.823469291778352</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="4"/>
+        <v>609.17653070822166</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="5"/>
+        <v>3920.3194223714245</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="2"/>
+        <v>6079.6805776285755</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46265</v>
+      </c>
+      <c r="B13" s="23">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>78.608528268940589</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="4"/>
+        <v>621.39147173105937</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="5"/>
+        <v>3298.927950640365</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>6701.0720493596345</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>5600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B14" s="22">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H14" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
+        <v>66.148658597886595</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="4"/>
+        <v>633.85134140211335</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="5"/>
+        <v>2665.0766092382519</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="2"/>
+        <v>7334.9233907617481</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>5126.6976567527154</v>
+        <v>2665.0766092382519</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1899,7 +1907,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4873.3023432472846</v>
+        <v>7334.9233907617481</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
